--- a/Content/Arena/List of Arenas.xlsx
+++ b/Content/Arena/List of Arenas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="108">
   <si>
     <t>擂台编号</t>
   </si>
@@ -65,7 +65,16 @@
     <t>攻擂中</t>
   </si>
   <si>
-    <t>视频链接</t>
+    <t>国内视频链接</t>
+  </si>
+  <si>
+    <t>国际视频链接</t>
+  </si>
+  <si>
+    <t>视频封面图片链接</t>
+  </si>
+  <si>
+    <t>首页展示顺序</t>
   </si>
   <si>
     <t>1</t>
@@ -101,7 +110,10 @@
     <t>私部署版：Claude Code +Kimi K2.5/Minimax M2.5/Qwen 3.5 + Metaso</t>
   </si>
   <si>
-    <t>https://rwai-dev.oss-cn-shanghai.aliyuncs.com/1.mov</t>
+    <t>https://www.bilibili.com/video/BV1FxFYzyEk8</t>
+  </si>
+  <si>
+    <t>https://rwai-dev.oss-cn-shanghai.aliyuncs.com/1.JPG</t>
   </si>
   <si>
     <t>2</t>
@@ -135,6 +147,9 @@
   </si>
   <si>
     <t>https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.mp4</t>
+  </si>
+  <si>
+    <t>https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.JPG</t>
   </si>
   <si>
     <t>3</t>
@@ -361,13 +376,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -381,6 +389,13 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -815,28 +830,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -960,11 +975,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1284,13 +1301,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="13" width="19" customWidth="1"/>
+    <col min="1" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="94.7857142857143" customWidth="1"/>
+    <col min="13" max="16" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13" customHeight="1" spans="1:13">
+    <row r="1" ht="13" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1330,505 +1349,536 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1" spans="1:13">
+    <row r="2" ht="25.5" customHeight="1" spans="1:16">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="4" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="P4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" t="s">
         <v>24</v>
       </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="3" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A3" t="s">
+    <row r="9" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>35</v>
+      <c r="L9" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="10" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>42</v>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
+    <row r="13" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" ht="25.5" customHeight="1" spans="1:16">
+      <c r="A14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
         <v>47</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" ht="25.5" customHeight="1" spans="1:13">
-      <c r="A14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1849,6 +1899,12 @@
       <formula1>"较优,中等"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" display="https://www.bilibili.com/video/BV1FxFYzyEk8"/>
+    <hyperlink ref="N2" r:id="rId1" display="https://www.bilibili.com/video/BV1FxFYzyEk8"/>
+    <hyperlink ref="M3" r:id="rId2" display="https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.mp4"/>
+    <hyperlink ref="N3" r:id="rId2" display="https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.mp4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/Content/Arena/List of Arenas.xlsx
+++ b/Content/Arena/List of Arenas.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="17900"/>
   </bookViews>
   <sheets>
-    <sheet name="数据表" sheetId="2" r:id="rId1"/>
+    <sheet name="数据表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
   <si>
     <t>擂台编号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>本周擂主</t>
   </si>
   <si>
+    <t>关联引用</t>
+  </si>
+  <si>
     <t>验证状态</t>
   </si>
   <si>
@@ -86,6 +89,11 @@
     <t>私部署版：Claude Code + GLM 5 + Metaso</t>
   </si>
   <si>
+    <t>Claude Code (by Anthropic) GitHub：https://github.com/anthropics/claude-code
+Metaso MCP (by 秘塔科技) 文档：https://www.modelscope.cn/mcp/servers/metasota/metaso-search
+GLM-5(by 智谱) GitHub：https://github.com/zai-org/GLM-5</t>
+  </si>
+  <si>
     <t>已验证</t>
   </si>
   <si>
@@ -125,6 +133,11 @@
     <t>云端版：Lovable + Kimi K2.5 + Claude Code</t>
   </si>
   <si>
+    <t>Lovable首页：https://lovable.dev/
+Claude Code (by Anthropic) GitHub：https://github.com/anthropics/claude-code
+Kimi-K2.5(by 月之暗面) GitHub：https://github.com/MoonshotAI/Kimi-K2.5</t>
+  </si>
+  <si>
     <t>0技术门槛1-2日内搭建出1个有基础互动能力的业务看板或网站Demo</t>
   </si>
   <si>
@@ -161,6 +174,13 @@
     <t>私部署版：LangChain + GLM 5+ Pydantic + unstructured + Faiss</t>
   </si>
   <si>
+    <t>LangChain（by LangChain） GitHub：https://github.com/langchain-ai/langchain
+Pydantic（by Pydantic） Github: https://github.com/pydantic/pydantic
+unstructured（by Unstructured.io） Github : https://github.com/Unstructured-IO/unstructured
+Faiss（by Facebook） Github: https://github.com/facebookresearch/faiss
+GLM-5(by 智谱) GitHub：https://github.com/zai-org/GLM-5</t>
+  </si>
+  <si>
     <t>一周构建1个完整性检查与风险评估的文档解析系统Demo</t>
   </si>
   <si>
@@ -182,6 +202,13 @@
     <t>私部署版：Claude Code + Claude Opus 4.6 + FFmpeg + FunASR + PaddleSpeech</t>
   </si>
   <si>
+    <t>Claude Code (by Anthropic) GitHub：https://github.com/anthropics/claude-code
+FFmpeg 官网：https://www.ffmpeg.org/
+FunASR(by 阿里) GitHub：https://github.com/modelscope/FunASR
+PaddleSpeech(by 百度) GitHub：https://github.com/PaddlePaddle/PaddleSpeech
+Claude Opus 4.6(by Anthropic) GitHub：https://www.anthropic.com/claude/opus</t>
+  </si>
+  <si>
     <t>最快2.5日内生成1个企业级产品或功能简要演示视频</t>
   </si>
   <si>
@@ -203,6 +230,10 @@
     <t>私部署版：BISHENG + GLM 5</t>
   </si>
   <si>
+    <t>BISHENG(by 毕昇) GitHub：https://github.com/dataelement/bisheng
+GLM-5(by 智谱) GitHub：https://github.com/zai-org/GLM-5</t>
+  </si>
+  <si>
     <t>一周搭建一个儿童教育应用Demo</t>
   </si>
   <si>
@@ -224,6 +255,11 @@
     <t>私部署版：Autogluon + Neuralforecast + EMTSF</t>
   </si>
   <si>
+    <t>Autogluon （by AWS AI） GitHub: https://github.com/autogluon/autogluon
+Neuralforecast （by Nixtla） GitHub: https://github.com/Nixtla/neuralforecast
+ETT数据集SOTA 模型：https://arxiv.org/pdf/2510.23396</t>
+  </si>
+  <si>
     <t>一周用低代码快速构建并验证一个面向能源领域的长时间序列预测系统Demo</t>
   </si>
   <si>
@@ -245,6 +281,10 @@
     <t>私部署版：Gemini CLI + Gemini 3.1 Pro</t>
   </si>
   <si>
+    <t>Gemini CLI(by Google) GitHub：https://github.com/google-gemini/gemini-cli
+Gemini 3.1 Pro(by Google) 官网：https://deepmind.google/models/gemini/pro/</t>
+  </si>
+  <si>
     <t>一周快速构建1个智能文档翻译Demo</t>
   </si>
   <si>
@@ -257,6 +297,9 @@
     <t>私部署版：BISHENG</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>验证中</t>
   </si>
   <si>
@@ -278,6 +321,11 @@
     <t>私部署版：Ultralytics YOLO （YOLO 11）+ Triton + Perf Analyzer</t>
   </si>
   <si>
+    <t>Ultralytics YOLO （by Ultralytics） : https://docs.ultralytics.com/models/yolo11/
+Triton （by NVIDIA） GitHub : https://github.com/triton-inference-server/server/blob/main/docs/user_guide/model_configuration.md
+Perf Analyzer （by NVIDIA） GitHub: https://github.com/triton-inference-server/perf_analyzer</t>
+  </si>
+  <si>
     <t>一周构建1个高精度、含数据流闭环、具备自进化能力的通用目标检测系统Demo</t>
   </si>
   <si>
@@ -296,6 +344,10 @@
     <t>私部署版：XiYan-SQL（QwenCoder-32B）</t>
   </si>
   <si>
+    <t>XiYan-SQL(by 阿里) Github：https://github.com/XGenerationLab/XiYan-SQL
+XiYanSQL-QwenCoder(by 阿里) GitHub：https://github.com/XGenerationLab/XiYanSQL-QwenCoder</t>
+  </si>
+  <si>
     <t>快速搭建一个大模型，通过对话生成SQL脚本</t>
   </si>
   <si>
@@ -314,6 +366,10 @@
     <t>私部署版：Coze + GLM 5</t>
   </si>
   <si>
+    <t>Coze （by 字节跳动） : https://www.coze.cn/
+GLM-5(by 智谱) GitHub：https://github.com/zai-org/GLM-5</t>
+  </si>
+  <si>
     <t>一周基于低代码构建一个具备主动追问与推荐能力的对话式助手Demo</t>
   </si>
   <si>
@@ -333,6 +389,10 @@
   </si>
   <si>
     <t>私部署版：LangChain + GLM 5</t>
+  </si>
+  <si>
+    <t>LangChain（by LangChain） GitHub：https://github.com/langchain-ai/langchain
+GLM-5(by 智谱) GitHub：https://github.com/zai-org/GLM-5</t>
   </si>
   <si>
     <t>一周低代码构建具备多源数据整合、合规校验、信贷报告一键生成能力的银行智能信贷系统Demo</t>
@@ -830,148 +890,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1301,15 +1361,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="94.7857142857143" customWidth="1"/>
-    <col min="13" max="16" width="19" customWidth="1"/>
+    <col min="1" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="19.9375" customWidth="1"/>
+    <col min="5" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="94.7857142857143" customWidth="1"/>
+    <col min="14" max="17" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13" customHeight="1" spans="1:16">
+    <row r="1" ht="13" customHeight="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +1381,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1358,552 +1420,594 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1" spans="1:16">
+    <row r="2" ht="25.5" customHeight="1" spans="1:17">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="4" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="Q4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="I8" t="s">
         <v>25</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="L8" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="M8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" t="s">
         <v>27</v>
       </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" t="s">
-        <v>29</v>
+      <c r="M9" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="3" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
+    <row r="10" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" t="s">
         <v>25</v>
       </c>
-      <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" t="s">
+        <v>109</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" t="s">
         <v>40</v>
       </c>
-      <c r="P3" t="s">
-        <v>16</v>
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
+    <row r="13" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I13" t="s">
         <v>25</v>
       </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="3"/>
-      <c r="P4" t="s">
-        <v>41</v>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="14" ht="25.5" customHeight="1" spans="1:17">
+      <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" t="s">
+        <v>109</v>
+      </c>
+      <c r="I14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="s">
         <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" t="s">
-        <v>97</v>
-      </c>
-      <c r="H13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" ht="25.5" customHeight="1" spans="1:16">
-      <c r="A14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" sqref="D2:D13">
+    <dataValidation type="list" sqref="E2:E13">
       <formula1>"已验证,验证中"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H13">
+    <dataValidation type="list" sqref="I2:I13">
       <formula1>"一周,1~2天"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I13">
+    <dataValidation type="list" sqref="J2:J13">
       <formula1>"较高,很高,中等,较低"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J13">
+    <dataValidation type="list" sqref="K2:K13">
       <formula1>"较高,较低"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K2:K13">
+    <dataValidation type="list" sqref="L2:L13">
       <formula1>"较优,中等"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" display="https://www.bilibili.com/video/BV1FxFYzyEk8"/>
     <hyperlink ref="N2" r:id="rId1" display="https://www.bilibili.com/video/BV1FxFYzyEk8"/>
-    <hyperlink ref="M3" r:id="rId2" display="https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.mp4"/>
+    <hyperlink ref="O2" r:id="rId1" display="https://www.bilibili.com/video/BV1FxFYzyEk8"/>
     <hyperlink ref="N3" r:id="rId2" display="https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.mp4"/>
+    <hyperlink ref="O3" r:id="rId2" display="https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.mp4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Content/Arena/List of Arenas.xlsx
+++ b/Content/Arena/List of Arenas.xlsx
@@ -507,11 +507,7 @@
           <t>https://www.bilibili.com/video/BV1FxFYzyEk8</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>https://rwai-dev.oss-cn-shanghai.aliyuncs.com/1.JPG</t>
-        </is>
-      </c>
+      <c r="P2"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>2</t>
@@ -596,11 +592,7 @@
           <t>https://www.bilibili.com/video/BV1qxwXzAEME</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>https://rwai-dev.oss-cn-shanghai.aliyuncs.com/2.JPG</t>
-        </is>
-      </c>
+      <c r="P3"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>

--- a/Content/Arena/List of Arenas.xlsx
+++ b/Content/Arena/List of Arenas.xlsx
@@ -986,7 +986,11 @@
           <t>私部署版：BISHENG</t>
         </is>
       </c>
-      <c r="D9"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BISHENG GitHub：https://github.com/dataelement/bisheng</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>验证中</t>
